--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260826.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260826.xlsx
@@ -909,17 +909,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>545,014,213</t>
+          <t>61,506,750</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -931,17 +931,17 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>61,506,750</t>
+          <t>545,014,213</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>26,558,536</t>
+          <t>2,187,587</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>2,187,587</t>
+          <t>26,558,536</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>275,200,160</t>
+          <t>70,267,242</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>70,267,242</t>
+          <t>275,200,160</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>永豐金</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>366,490,022</t>
+          <t>304,816,535</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>永豐金</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>304,816,535</t>
+          <t>366,490,022</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>7,996,031</t>
+          <t>4,160,749</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>4,160,749</t>
+          <t>7,996,031</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>1,840,039</t>
+          <t>10,747,372</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>10,747,372</t>
+          <t>1,840,039</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
